--- a/filer/33054173_winum.xlsx
+++ b/filer/33054173_winum.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse B · Andre erklæringer uden sikkerh</t>
         </is>
       </c>
     </row>

--- a/filer/33054173_winum.xlsx
+++ b/filer/33054173_winum.xlsx
@@ -190,8 +190,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +644,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1498,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -1818,49 +1818,49 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B29" s="8">
         <f>'balance_raw_33054173'!$B$8</f>
         <v/>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="8">
         <f>'balance_raw_33054173'!$C$8</f>
         <v/>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="8">
         <f>'balance_raw_33054173'!$D$8</f>
         <v/>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <f>'balance_raw_33054173'!$E$8</f>
         <v/>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="8">
         <f>'balance_raw_33054173'!$F$8</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" s="12">
+      <c r="H29" s="9">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="9">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="9">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="9">
         <f>IFERROR(E29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="9">
         <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
@@ -1868,7 +1868,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Råvarer og hjælpematerialer</t>
+          <t>Deposita</t>
         </is>
       </c>
       <c r="B30" s="5">
@@ -1914,145 +1914,145 @@
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Varer under fremstilling</t>
-        </is>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
         <f>'balance_raw_33054173'!$B$10</f>
         <v/>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="11">
         <f>'balance_raw_33054173'!$C$10</f>
         <v/>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="11">
         <f>'balance_raw_33054173'!$D$10</f>
         <v/>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="11">
         <f>'balance_raw_33054173'!$E$10</f>
         <v/>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="11">
         <f>'balance_raw_33054173'!$F$10</f>
         <v/>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" s="9">
+      <c r="H31" s="12">
         <f>IFERROR(B31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="12">
         <f>IFERROR(C31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="12">
         <f>IFERROR(D31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="12">
         <f>IFERROR(E31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="12">
         <f>IFERROR(F31/$B$31*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Færdigvarer og handelsvarer</t>
-        </is>
-      </c>
-      <c r="B32" s="5">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
         <f>'balance_raw_33054173'!$B$11</f>
         <v/>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="11">
         <f>'balance_raw_33054173'!$C$11</f>
         <v/>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="11">
         <f>'balance_raw_33054173'!$D$11</f>
         <v/>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="11">
         <f>'balance_raw_33054173'!$E$11</f>
         <v/>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="11">
         <f>'balance_raw_33054173'!$F$11</f>
         <v/>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" s="6">
+      <c r="H32" s="12">
         <f>IFERROR(B32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="12">
         <f>IFERROR(C32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="12">
         <f>IFERROR(D32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="12">
         <f>IFERROR(E32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="12">
         <f>IFERROR(F32/$B$32*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B33" s="11">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B33" s="8">
         <f>'balance_raw_33054173'!$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="8">
         <f>'balance_raw_33054173'!$C$12</f>
         <v/>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="8">
         <f>'balance_raw_33054173'!$D$12</f>
         <v/>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="8">
         <f>'balance_raw_33054173'!$E$12</f>
         <v/>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="8">
         <f>'balance_raw_33054173'!$F$12</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="12">
+      <c r="H33" s="9">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="9">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="9">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="9">
         <f>IFERROR(E33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="9">
         <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
@@ -2060,7 +2060,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Varer under fremstilling</t>
         </is>
       </c>
       <c r="B34" s="5">
@@ -2108,7 +2108,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
       <c r="B35" s="8">
@@ -2154,49 +2154,49 @@
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B36" s="5">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
         <f>'balance_raw_33054173'!$B$15</f>
         <v/>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="11">
         <f>'balance_raw_33054173'!$C$15</f>
         <v/>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="11">
         <f>'balance_raw_33054173'!$D$15</f>
         <v/>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="11">
         <f>'balance_raw_33054173'!$E$15</f>
         <v/>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="11">
         <f>'balance_raw_33054173'!$F$15</f>
         <v/>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" s="6">
+      <c r="H36" s="12">
         <f>IFERROR(B36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="12">
         <f>IFERROR(C36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="12">
         <f>IFERROR(D36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="12">
         <f>IFERROR(E36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="12">
         <f>IFERROR(F36/$B$36*100,"")</f>
         <v/>
       </c>
@@ -2204,7 +2204,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B37" s="8">
@@ -2252,7 +2252,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B38" s="5">
@@ -2300,7 +2300,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -2348,7 +2348,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B40" s="5">
@@ -2394,49 +2394,49 @@
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B41" s="11">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B41" s="8">
         <f>'balance_raw_33054173'!$B$20</f>
         <v/>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="8">
         <f>'balance_raw_33054173'!$C$20</f>
         <v/>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="8">
         <f>'balance_raw_33054173'!$D$20</f>
         <v/>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="8">
         <f>'balance_raw_33054173'!$E$20</f>
         <v/>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="8">
         <f>'balance_raw_33054173'!$F$20</f>
         <v/>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="12">
+      <c r="H41" s="9">
         <f>IFERROR(B41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="9">
         <f>IFERROR(C41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="9">
         <f>IFERROR(D41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="9">
         <f>IFERROR(E41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="9">
         <f>IFERROR(F41/$B$41*100,"")</f>
         <v/>
       </c>
@@ -2444,7 +2444,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B42" s="5">
@@ -2492,7 +2492,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -2540,7 +2540,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Tilgodehavender</t>
         </is>
       </c>
       <c r="B44" s="11">
@@ -2586,239 +2586,239 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B45" s="8">
+        <f>'balance_raw_33054173'!$B$24</f>
+        <v/>
+      </c>
+      <c r="C45" s="8">
+        <f>'balance_raw_33054173'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D45" s="8">
+        <f>'balance_raw_33054173'!$D$24</f>
+        <v/>
+      </c>
+      <c r="E45" s="8">
+        <f>'balance_raw_33054173'!$E$24</f>
+        <v/>
+      </c>
+      <c r="F45" s="8">
+        <f>'balance_raw_33054173'!$F$24</f>
+        <v/>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" s="9">
+        <f>IFERROR(B45/$B$45*100,"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="9">
+        <f>IFERROR(C45/$B$45*100,"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="9">
+        <f>IFERROR(D45/$B$45*100,"")</f>
+        <v/>
+      </c>
+      <c r="K45" s="9">
+        <f>IFERROR(E45/$B$45*100,"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="9">
+        <f>IFERROR(F45/$B$45*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B46" s="5">
+        <f>'balance_raw_33054173'!$B$25</f>
+        <v/>
+      </c>
+      <c r="C46" s="5">
+        <f>'balance_raw_33054173'!$C$25</f>
+        <v/>
+      </c>
+      <c r="D46" s="5">
+        <f>'balance_raw_33054173'!$D$25</f>
+        <v/>
+      </c>
+      <c r="E46" s="5">
+        <f>'balance_raw_33054173'!$E$25</f>
+        <v/>
+      </c>
+      <c r="F46" s="5">
+        <f>'balance_raw_33054173'!$F$25</f>
+        <v/>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" s="6">
+        <f>IFERROR(B46/$B$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="6">
+        <f>IFERROR(C46/$B$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="6">
+        <f>IFERROR(D46/$B$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="6">
+        <f>IFERROR(E46/$B$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="6">
+        <f>IFERROR(F46/$B$46*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B47" s="11">
+        <f>'balance_raw_33054173'!$B$26</f>
+        <v/>
+      </c>
+      <c r="C47" s="11">
+        <f>'balance_raw_33054173'!$C$26</f>
+        <v/>
+      </c>
+      <c r="D47" s="11">
+        <f>'balance_raw_33054173'!$D$26</f>
+        <v/>
+      </c>
+      <c r="E47" s="11">
+        <f>'balance_raw_33054173'!$E$26</f>
+        <v/>
+      </c>
+      <c r="F47" s="11">
+        <f>'balance_raw_33054173'!$F$26</f>
+        <v/>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" s="12">
+        <f>IFERROR(B47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="12">
+        <f>IFERROR(C47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="12">
+        <f>IFERROR(D47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="12">
+        <f>IFERROR(E47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="12">
+        <f>IFERROR(F47/$B$47*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B45" s="11">
-        <f>'balance_raw_33054173'!$B$24</f>
-        <v/>
-      </c>
-      <c r="C45" s="11">
-        <f>'balance_raw_33054173'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D45" s="11">
-        <f>'balance_raw_33054173'!$D$24</f>
-        <v/>
-      </c>
-      <c r="E45" s="11">
-        <f>'balance_raw_33054173'!$E$24</f>
-        <v/>
-      </c>
-      <c r="F45" s="11">
-        <f>'balance_raw_33054173'!$F$24</f>
-        <v/>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="12">
-        <f>IFERROR(B45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="12">
-        <f>IFERROR(C45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="12">
-        <f>IFERROR(D45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="12">
-        <f>IFERROR(E45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="L45" s="12">
-        <f>IFERROR(F45/$B$45*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="B48" s="11">
+        <f>'balance_raw_33054173'!$B$27</f>
+        <v/>
+      </c>
+      <c r="C48" s="11">
+        <f>'balance_raw_33054173'!$C$27</f>
+        <v/>
+      </c>
+      <c r="D48" s="11">
+        <f>'balance_raw_33054173'!$D$27</f>
+        <v/>
+      </c>
+      <c r="E48" s="11">
+        <f>'balance_raw_33054173'!$E$27</f>
+        <v/>
+      </c>
+      <c r="F48" s="11">
+        <f>'balance_raw_33054173'!$F$27</f>
+        <v/>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" s="12">
+        <f>IFERROR(B48/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="12">
+        <f>IFERROR(C48/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="12">
+        <f>IFERROR(D48/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="12">
+        <f>IFERROR(E48/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="12">
+        <f>IFERROR(F48/$B$48*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>PASSIVER t.kr.</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C47" s="3" t="n">
+      <c r="B50" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="C50" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I47" s="3" t="n">
+      <c r="F50" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="I50" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="J50" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="K50" s="3" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B48" s="5">
-        <f>'balance_raw_33054173'!$B$25</f>
-        <v/>
-      </c>
-      <c r="C48" s="5">
-        <f>'balance_raw_33054173'!$C$25</f>
-        <v/>
-      </c>
-      <c r="D48" s="5">
-        <f>'balance_raw_33054173'!$D$25</f>
-        <v/>
-      </c>
-      <c r="E48" s="5">
-        <f>'balance_raw_33054173'!$E$25</f>
-        <v/>
-      </c>
-      <c r="F48" s="5">
-        <f>'balance_raw_33054173'!$F$25</f>
-        <v/>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="6">
-        <f>IFERROR(B48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="6">
-        <f>IFERROR(C48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="6">
-        <f>IFERROR(D48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="6">
-        <f>IFERROR(E48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="L48" s="6">
-        <f>IFERROR(F48/$B$48*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
-        <f>'balance_raw_33054173'!$B$26</f>
-        <v/>
-      </c>
-      <c r="C49" s="8">
-        <f>'balance_raw_33054173'!$C$26</f>
-        <v/>
-      </c>
-      <c r="D49" s="8">
-        <f>'balance_raw_33054173'!$D$26</f>
-        <v/>
-      </c>
-      <c r="E49" s="8">
-        <f>'balance_raw_33054173'!$E$26</f>
-        <v/>
-      </c>
-      <c r="F49" s="8">
-        <f>'balance_raw_33054173'!$F$26</f>
-        <v/>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="9">
-        <f>IFERROR(B49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="9">
-        <f>IFERROR(C49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="9">
-        <f>IFERROR(D49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="9">
-        <f>IFERROR(E49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="L49" s="9">
-        <f>IFERROR(F49/$B$49*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B50" s="5">
-        <f>'balance_raw_33054173'!$B$27</f>
-        <v/>
-      </c>
-      <c r="C50" s="5">
-        <f>'balance_raw_33054173'!$C$27</f>
-        <v/>
-      </c>
-      <c r="D50" s="5">
-        <f>'balance_raw_33054173'!$D$27</f>
-        <v/>
-      </c>
-      <c r="E50" s="5">
-        <f>'balance_raw_33054173'!$E$27</f>
-        <v/>
-      </c>
-      <c r="F50" s="5">
-        <f>'balance_raw_33054173'!$F$27</f>
-        <v/>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="6">
-        <f>IFERROR(B50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="6">
-        <f>IFERROR(C50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="6">
-        <f>IFERROR(D50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="6">
-        <f>IFERROR(E50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="L50" s="6">
-        <f>IFERROR(F50/$B$50*100,"")</f>
-        <v/>
+      <c r="L50" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Selskabskapital</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2866,7 +2866,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B52" s="5">
@@ -2914,7 +2914,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B53" s="8">
@@ -2960,49 +2960,49 @@
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B54" s="11">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B54" s="5">
         <f>'balance_raw_33054173'!$B$31</f>
         <v/>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="5">
         <f>'balance_raw_33054173'!$C$31</f>
         <v/>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="5">
         <f>'balance_raw_33054173'!$D$31</f>
         <v/>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="5">
         <f>'balance_raw_33054173'!$E$31</f>
         <v/>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="5">
         <f>'balance_raw_33054173'!$F$31</f>
         <v/>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="12">
+      <c r="H54" s="6">
         <f>IFERROR(B54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="I54" s="12">
+      <c r="I54" s="6">
         <f>IFERROR(C54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="J54" s="12">
+      <c r="J54" s="6">
         <f>IFERROR(D54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="K54" s="12">
+      <c r="K54" s="6">
         <f>IFERROR(E54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="L54" s="12">
+      <c r="L54" s="6">
         <f>IFERROR(F54/$B$54*100,"")</f>
         <v/>
       </c>
@@ -3010,7 +3010,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -3058,7 +3058,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B56" s="5">
@@ -3104,49 +3104,49 @@
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B57" s="11">
         <f>'balance_raw_33054173'!$B$34</f>
         <v/>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="11">
         <f>'balance_raw_33054173'!$C$34</f>
         <v/>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="11">
         <f>'balance_raw_33054173'!$D$34</f>
         <v/>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="11">
         <f>'balance_raw_33054173'!$E$34</f>
         <v/>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="11">
         <f>'balance_raw_33054173'!$F$34</f>
         <v/>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" s="9">
+      <c r="H57" s="12">
         <f>IFERROR(B57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="12">
         <f>IFERROR(C57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="12">
         <f>IFERROR(D57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="K57" s="9">
+      <c r="K57" s="12">
         <f>IFERROR(E57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="L57" s="9">
+      <c r="L57" s="12">
         <f>IFERROR(F57/$B$57*100,"")</f>
         <v/>
       </c>
@@ -3154,7 +3154,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B58" s="5">
@@ -3202,7 +3202,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B59" s="8">
@@ -3250,7 +3250,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B60" s="5">
@@ -3298,7 +3298,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B61" s="8">
@@ -3346,7 +3346,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3394,7 +3394,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B63" s="8">
@@ -3442,7 +3442,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3490,7 +3490,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B65" s="8">
@@ -3536,584 +3536,735 @@
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B66" s="5">
+        <f>'balance_raw_33054173'!$B$43</f>
+        <v/>
+      </c>
+      <c r="C66" s="5">
+        <f>'balance_raw_33054173'!$C$43</f>
+        <v/>
+      </c>
+      <c r="D66" s="5">
+        <f>'balance_raw_33054173'!$D$43</f>
+        <v/>
+      </c>
+      <c r="E66" s="5">
+        <f>'balance_raw_33054173'!$E$43</f>
+        <v/>
+      </c>
+      <c r="F66" s="5">
+        <f>'balance_raw_33054173'!$F$43</f>
+        <v/>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="6">
+        <f>IFERROR(B66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="6">
+        <f>IFERROR(C66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="6">
+        <f>IFERROR(D66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="6">
+        <f>IFERROR(E66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="6">
+        <f>IFERROR(F66/$B$66*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
+        <f>'balance_raw_33054173'!$B$44</f>
+        <v/>
+      </c>
+      <c r="C67" s="8">
+        <f>'balance_raw_33054173'!$C$44</f>
+        <v/>
+      </c>
+      <c r="D67" s="8">
+        <f>'balance_raw_33054173'!$D$44</f>
+        <v/>
+      </c>
+      <c r="E67" s="8">
+        <f>'balance_raw_33054173'!$E$44</f>
+        <v/>
+      </c>
+      <c r="F67" s="8">
+        <f>'balance_raw_33054173'!$F$44</f>
+        <v/>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" s="9">
+        <f>IFERROR(B67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="9">
+        <f>IFERROR(C67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="9">
+        <f>IFERROR(D67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="9">
+        <f>IFERROR(E67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="9">
+        <f>IFERROR(F67/$B$67*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B68" s="5">
+        <f>'balance_raw_33054173'!$B$45</f>
+        <v/>
+      </c>
+      <c r="C68" s="5">
+        <f>'balance_raw_33054173'!$C$45</f>
+        <v/>
+      </c>
+      <c r="D68" s="5">
+        <f>'balance_raw_33054173'!$D$45</f>
+        <v/>
+      </c>
+      <c r="E68" s="5">
+        <f>'balance_raw_33054173'!$E$45</f>
+        <v/>
+      </c>
+      <c r="F68" s="5">
+        <f>'balance_raw_33054173'!$F$45</f>
+        <v/>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="6">
+        <f>IFERROR(B68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="6">
+        <f>IFERROR(C68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="6">
+        <f>IFERROR(D68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="6">
+        <f>IFERROR(E68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="6">
+        <f>IFERROR(F68/$B$68*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B66" s="11">
-        <f>'balance_raw_33054173'!$B$43</f>
-        <v/>
-      </c>
-      <c r="C66" s="11">
-        <f>'balance_raw_33054173'!$C$43</f>
-        <v/>
-      </c>
-      <c r="D66" s="11">
-        <f>'balance_raw_33054173'!$D$43</f>
-        <v/>
-      </c>
-      <c r="E66" s="11">
-        <f>'balance_raw_33054173'!$E$43</f>
-        <v/>
-      </c>
-      <c r="F66" s="11">
-        <f>'balance_raw_33054173'!$F$43</f>
-        <v/>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" s="12">
-        <f>IFERROR(B66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="12">
-        <f>IFERROR(C66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="12">
-        <f>IFERROR(D66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="K66" s="12">
-        <f>IFERROR(E66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="L66" s="12">
-        <f>IFERROR(F66/$B$66*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="B69" s="11">
+        <f>'balance_raw_33054173'!$B$46</f>
+        <v/>
+      </c>
+      <c r="C69" s="11">
+        <f>'balance_raw_33054173'!$C$46</f>
+        <v/>
+      </c>
+      <c r="D69" s="11">
+        <f>'balance_raw_33054173'!$D$46</f>
+        <v/>
+      </c>
+      <c r="E69" s="11">
+        <f>'balance_raw_33054173'!$E$46</f>
+        <v/>
+      </c>
+      <c r="F69" s="11">
+        <f>'balance_raw_33054173'!$F$46</f>
+        <v/>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="12">
+        <f>IFERROR(B69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="12">
+        <f>IFERROR(C69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="12">
+        <f>IFERROR(D69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="12">
+        <f>IFERROR(E69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="12">
+        <f>IFERROR(F69/$B$69*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B67" s="11">
-        <f>'balance_raw_33054173'!$B$44</f>
-        <v/>
-      </c>
-      <c r="C67" s="11">
-        <f>'balance_raw_33054173'!$C$44</f>
-        <v/>
-      </c>
-      <c r="D67" s="11">
-        <f>'balance_raw_33054173'!$D$44</f>
-        <v/>
-      </c>
-      <c r="E67" s="11">
-        <f>'balance_raw_33054173'!$E$44</f>
-        <v/>
-      </c>
-      <c r="F67" s="11">
-        <f>'balance_raw_33054173'!$F$44</f>
-        <v/>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" s="12">
-        <f>IFERROR(B67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="I67" s="12">
-        <f>IFERROR(C67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="12">
-        <f>IFERROR(D67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="K67" s="12">
-        <f>IFERROR(E67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="L67" s="12">
-        <f>IFERROR(F67/$B$67*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="B70" s="11">
+        <f>'balance_raw_33054173'!$B$47</f>
+        <v/>
+      </c>
+      <c r="C70" s="11">
+        <f>'balance_raw_33054173'!$C$47</f>
+        <v/>
+      </c>
+      <c r="D70" s="11">
+        <f>'balance_raw_33054173'!$D$47</f>
+        <v/>
+      </c>
+      <c r="E70" s="11">
+        <f>'balance_raw_33054173'!$E$47</f>
+        <v/>
+      </c>
+      <c r="F70" s="11">
+        <f>'balance_raw_33054173'!$F$47</f>
+        <v/>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="12">
+        <f>IFERROR(B70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="12">
+        <f>IFERROR(C70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="12">
+        <f>IFERROR(D70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="K70" s="12">
+        <f>IFERROR(E70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="L70" s="12">
+        <f>IFERROR(F70/$B$70*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B68" s="11">
-        <f>'balance_raw_33054173'!$B$45</f>
-        <v/>
-      </c>
-      <c r="C68" s="11">
-        <f>'balance_raw_33054173'!$C$45</f>
-        <v/>
-      </c>
-      <c r="D68" s="11">
-        <f>'balance_raw_33054173'!$D$45</f>
-        <v/>
-      </c>
-      <c r="E68" s="11">
-        <f>'balance_raw_33054173'!$E$45</f>
-        <v/>
-      </c>
-      <c r="F68" s="11">
-        <f>'balance_raw_33054173'!$F$45</f>
-        <v/>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" s="12">
-        <f>IFERROR(B68/$B$68*100,"")</f>
-        <v/>
-      </c>
-      <c r="I68" s="12">
-        <f>IFERROR(C68/$B$68*100,"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="12">
-        <f>IFERROR(D68/$B$68*100,"")</f>
-        <v/>
-      </c>
-      <c r="K68" s="12">
-        <f>IFERROR(E68/$B$68*100,"")</f>
-        <v/>
-      </c>
-      <c r="L68" s="12">
-        <f>IFERROR(F68/$B$68*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="B71" s="11">
+        <f>'balance_raw_33054173'!$B$48</f>
+        <v/>
+      </c>
+      <c r="C71" s="11">
+        <f>'balance_raw_33054173'!$C$48</f>
+        <v/>
+      </c>
+      <c r="D71" s="11">
+        <f>'balance_raw_33054173'!$D$48</f>
+        <v/>
+      </c>
+      <c r="E71" s="11">
+        <f>'balance_raw_33054173'!$E$48</f>
+        <v/>
+      </c>
+      <c r="F71" s="11">
+        <f>'balance_raw_33054173'!$F$48</f>
+        <v/>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="12">
+        <f>IFERROR(B71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="12">
+        <f>IFERROR(C71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="12">
+        <f>IFERROR(D71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="K71" s="12">
+        <f>IFERROR(E71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="L71" s="12">
+        <f>IFERROR(F71/$B$71*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C70" s="3" t="n">
+      <c r="B73" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="C73" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="D73" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="E73" s="3" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="F73" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B71" s="8">
+      <c r="B74" s="5">
         <f>'res_raw_33054173'!$B$19</f>
         <v/>
       </c>
-      <c r="C71" s="8">
+      <c r="C74" s="5">
         <f>'res_raw_33054173'!$C$19</f>
         <v/>
       </c>
-      <c r="D71" s="8">
+      <c r="D74" s="5">
         <f>'res_raw_33054173'!$D$19</f>
         <v/>
       </c>
-      <c r="E71" s="8">
+      <c r="E74" s="5">
         <f>'res_raw_33054173'!$E$19</f>
         <v/>
       </c>
-      <c r="F71" s="8">
+      <c r="F74" s="5">
         <f>'res_raw_33054173'!$F$19</f>
         <v/>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" s="9">
-        <f>IFERROR(B71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="I71" s="9">
-        <f>IFERROR(C71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="9">
-        <f>IFERROR(D71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="K71" s="9">
-        <f>IFERROR(E71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="L71" s="9">
-        <f>IFERROR(F71/$B$71*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B72" s="5">
-        <f>'res_raw_33054173'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C72" s="5">
-        <f>'res_raw_33054173'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D72" s="5">
-        <f>'res_raw_33054173'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E72" s="5">
-        <f>'res_raw_33054173'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F72" s="5">
-        <f>'res_raw_33054173'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" s="6">
-        <f>IFERROR(B72/$B$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="I72" s="6">
-        <f>IFERROR(C72/$B$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="J72" s="6">
-        <f>IFERROR(D72/$B$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="K72" s="6">
-        <f>IFERROR(E72/$B$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="L72" s="6">
-        <f>IFERROR(F72/$B$72*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>2024</v>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="6">
+        <f>IFERROR(B74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="6">
+        <f>IFERROR(C74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6">
+        <f>IFERROR(D74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="6">
+        <f>IFERROR(E74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="6">
+        <f>IFERROR(F74/$B$74*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C75" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E75" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F75" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$45*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B76" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C76" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E76" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F76" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B77" s="13">
-        <f>IFERROR($B$4/$B$45,"")</f>
-        <v/>
-      </c>
-      <c r="C77" s="13">
-        <f>IFERROR($C$4/$C$45,"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="13">
-        <f>IFERROR($D$4/$D$45,"")</f>
-        <v/>
-      </c>
-      <c r="E77" s="13">
-        <f>IFERROR($E$4/$E$45,"")</f>
-        <v/>
-      </c>
-      <c r="F77" s="13">
-        <f>IFERROR($F$4/$F$45,"")</f>
-        <v/>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
+        <f>'res_raw_33054173'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C75" s="8">
+        <f>'res_raw_33054173'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D75" s="8">
+        <f>'res_raw_33054173'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E75" s="8">
+        <f>'res_raw_33054173'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F75" s="8">
+        <f>'res_raw_33054173'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="9">
+        <f>IFERROR(B75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="9">
+        <f>IFERROR(C75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="9">
+        <f>IFERROR(D75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="K75" s="9">
+        <f>IFERROR(E75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="9">
+        <f>IFERROR(F75/$B$75*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B78" s="14">
-        <f>IFERROR($B$18/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="C78" s="14">
-        <f>IFERROR($C$18/$C$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="14">
-        <f>IFERROR($D$18/$D$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="E78" s="14">
-        <f>IFERROR($E$18/$E$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="F78" s="14">
-        <f>IFERROR($F$18/$F$54*100,"")</f>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B78" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="E78" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="F78" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$48*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B79" s="13">
-        <f>IFERROR($B$16/($B$68-$B$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C79" s="13">
-        <f>IFERROR($C$16/($C$68-$C$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="13">
-        <f>IFERROR($D$16/($D$68-$D$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="13">
-        <f>IFERROR($E$16/($E$68-$E$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F79" s="13">
-        <f>IFERROR($F$16/($F$68-$F$54)*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B79" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B80" s="14">
-        <f>IFERROR($B$54/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="14">
-        <f>IFERROR($C$54/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="14">
-        <f>IFERROR($D$54/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="14">
-        <f>IFERROR($E$54/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="14">
-        <f>IFERROR($F$54/$F$45*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>IFERROR($B$4/$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="13">
+        <f>IFERROR($C$4/$C$48,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="13">
+        <f>IFERROR($D$4/$D$48,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="13">
+        <f>IFERROR($E$4/$E$48,"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="13">
+        <f>IFERROR($F$4/$F$48,"")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B81" s="13">
-        <f>IFERROR(($B$68-$B$54)/$B$54,"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="13">
-        <f>IFERROR(($C$68-$C$54)/$C$54,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="13">
-        <f>IFERROR(($D$68-$D$54)/$D$54,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="13">
-        <f>IFERROR(($E$68-$E$54)/$E$54,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="13">
-        <f>IFERROR(($F$68-$F$54)/$F$54,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B81" s="14">
+        <f>IFERROR($B$18/$B$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="14">
+        <f>IFERROR($C$18/$C$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="14">
+        <f>IFERROR($D$18/$D$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>IFERROR($E$18/$E$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="14">
+        <f>IFERROR($F$18/$F$57*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B82" s="14">
-        <f>IFERROR($B$44/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="14">
-        <f>IFERROR($C$44/$C$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="14">
-        <f>IFERROR($D$44/$D$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="14">
-        <f>IFERROR($E$44/$E$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="14">
-        <f>IFERROR($F$44/$F$66*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B82" s="13">
+        <f>IFERROR($B$16/($B$71-$B$57)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="13">
+        <f>IFERROR($C$16/($C$71-$C$57)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="13">
+        <f>IFERROR($D$16/($D$71-$D$57)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="13">
+        <f>IFERROR($E$16/($E$71-$E$57)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="13">
+        <f>IFERROR($F$16/($F$71-$F$57)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B83" s="13">
-        <f>IFERROR(B75-B79,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="13">
-        <f>IFERROR(C75-C79,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="13">
-        <f>IFERROR(D75-D79,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="13">
-        <f>IFERROR(E75-E79,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="13">
-        <f>IFERROR(F75-F79,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B83" s="14">
+        <f>IFERROR($B$57/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="14">
+        <f>IFERROR($C$57/$C$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="14">
+        <f>IFERROR($D$57/$D$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>IFERROR($E$57/$E$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="14">
+        <f>IFERROR($F$57/$F$48*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B84" s="14">
-        <f>IFERROR(($B$68-$B$54)/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="14">
-        <f>IFERROR(($C$68-$C$54)/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="14">
-        <f>IFERROR(($D$68-$D$54)/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="14">
-        <f>IFERROR(($E$68-$E$54)/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="14">
-        <f>IFERROR(($F$68-$F$54)/$F$45*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B84" s="13">
+        <f>IFERROR(($B$71-$B$57)/$B$57,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="13">
+        <f>IFERROR(($C$71-$C$57)/$C$57,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="13">
+        <f>IFERROR(($D$71-$D$57)/$D$57,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="13">
+        <f>IFERROR(($E$71-$E$57)/$E$57,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="13">
+        <f>IFERROR(($F$71-$F$57)/$F$57,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B85" s="14">
+        <f>IFERROR($B$47/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="14">
+        <f>IFERROR($C$47/$C$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="14">
+        <f>IFERROR($D$47/$D$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>IFERROR($E$47/$E$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="14">
+        <f>IFERROR($F$47/$F$69*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B86" s="13">
+        <f>IFERROR(B78-B82,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="13">
+        <f>IFERROR(C78-C82,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="13">
+        <f>IFERROR(D78-D82,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="13">
+        <f>IFERROR(E78-E82,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="13">
+        <f>IFERROR(F78-F82,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B87" s="14">
+        <f>IFERROR(($B$71-$B$57)/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="14">
+        <f>IFERROR(($C$71-$C$57)/$C$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="14">
+        <f>IFERROR(($D$71-$D$57)/$D$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="14">
+        <f>IFERROR(($E$71-$E$57)/$E$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="14">
+        <f>IFERROR(($F$71-$F$57)/$F$48*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B85" s="13">
-        <f>IFERROR($B$29/($B$54+0)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="13">
-        <f>IFERROR($C$29/($C$54+0)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="13">
-        <f>IFERROR($D$29/($D$54+0)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="13">
-        <f>IFERROR($E$29/($E$54+0)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="13">
-        <f>IFERROR($F$29/($F$54+0)*100,"")</f>
-        <v/>
+      <c r="B88" s="13">
+        <f>IFERROR($B$32/($B$57+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="13">
+        <f>IFERROR($C$32/($C$57+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="13">
+        <f>IFERROR($D$32/($D$57+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="13">
+        <f>IFERROR($E$32/($E$57+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="13">
+        <f>IFERROR($F$32/($F$57+0)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4145,19 +4296,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4215,19 +4366,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>1357</v>
+        <v>1095</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>1095</v>
+        <v>1507</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1507</v>
+        <v>1493</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>1493</v>
+        <v>1250</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>1250</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="7">
@@ -4237,19 +4388,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>839</v>
+        <v>981</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1120</v>
+        <v>1053</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>1053</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="8">
@@ -4266,19 +4417,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -4287,9 +4438,7 @@
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
@@ -4302,19 +4451,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>165</v>
+        <v>408</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>408</v>
+        <v>260</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>260</v>
+        <v>88</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>88</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="12">
@@ -4336,17 +4485,17 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4359,16 +4508,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="16" t="n">
-        <v>7</v>
-      </c>
       <c r="E14" s="16" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -4390,19 +4539,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>472</v>
+        <v>154</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>154</v>
+        <v>400</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>64</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="17">
@@ -4412,19 +4561,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>15</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="18">
@@ -4434,19 +4583,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>471</v>
+        <v>118</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>118</v>
+        <v>313</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>313</v>
+        <v>192</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>49</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="19">
@@ -4494,7 +4643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4512,19 +4661,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4533,9 +4682,7 @@
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B2" s="16" t="n"/>
       <c r="C2" s="16" t="n"/>
       <c r="D2" s="16" t="n"/>
       <c r="E2" s="16" t="n"/>
@@ -4560,19 +4707,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>31</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
@@ -4582,19 +4729,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>702</v>
+        <v>836</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>836</v>
+        <v>745</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>745</v>
+        <v>612</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>612</v>
+        <v>527</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>527</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6">
@@ -4616,217 +4763,199 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>745</v>
+        <v>946</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>946</v>
+        <v>827</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>827</v>
+        <v>667</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>667</v>
+        <v>558</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>558</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>745</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>946</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>827</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>667</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>558</v>
-      </c>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Råvarer og hjælpematerialer</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>121</v>
-      </c>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
       <c r="F9" s="16" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Varer under fremstilling</t>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="F10" s="16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Færdigvarer og handelsvarer</t>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>50</v>
+        <v>946</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>210</v>
+        <v>667</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>690</v>
+        <v>558</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>525</v>
+        <v>675</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>180</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>390</v>
+        <v>121</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>811</v>
+        <v>135</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>660</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>275</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>236</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>161</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>351</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>320</v>
-      </c>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>210</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>690</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>525</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+        <v>180</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>390</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>811</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>660</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>654</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>68</v>
+        <v>351</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>65</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>128</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>93</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>4</v>
-      </c>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B18" s="16" t="n"/>
@@ -4838,41 +4967,51 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>419</v>
+        <v>93</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>403</v>
+        <v>14</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>243</v>
+        <v>11</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>432</v>
+        <v>4</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>389</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B21" s="16" t="n"/>
@@ -4884,131 +5023,141 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>475</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>483</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>469</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>297</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>588</v>
-      </c>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Tilgodehavender</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>1123</v>
+        <v>403</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>1066</v>
+        <v>243</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1101</v>
+        <v>432</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>1540</v>
+        <v>389</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1637</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>1868</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>2012</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>1928</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>2207</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>2195</v>
-      </c>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
+          <t>Likvide beholdninger</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>125</v>
+        <v>483</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>125</v>
+        <v>469</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>125</v>
+        <v>297</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>125</v>
+        <v>588</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>125</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>1101</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>1540</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>1405</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>2207</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>2195</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>2080</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B29" s="16" t="n"/>
@@ -5020,51 +5169,31 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>634</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>752</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>1065</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>1257</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>1307</v>
-      </c>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>759</v>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>877</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>1190</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>1382</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>1432</v>
-      </c>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B32" s="16" t="n"/>
@@ -5076,31 +5205,51 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>752</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>1257</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>1307</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>1252</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>877</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>1382</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>1432</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>1377</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B35" s="16" t="n"/>
@@ -5112,195 +5261,233 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>216</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>520</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>281</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>113</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>113</v>
-      </c>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>383</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>247</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>258</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>269</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>324</v>
-      </c>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>520</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>281</v>
+      </c>
       <c r="D39" s="16" t="n">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n">
+        <v>247</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>258</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>269</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>324</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>328</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>510</v>
+        <v>19</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>191</v>
+        <v>2</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>385</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>319</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>191</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>385</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>319</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="C43" s="16" t="n">
+      <c r="B46" s="16" t="n">
         <v>1135</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="C46" s="16" t="n">
         <v>738</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="D46" s="16" t="n">
         <v>824</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="E46" s="16" t="n">
         <v>764</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="F46" s="16" t="n">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B47" s="16" t="n">
         <v>1135</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C47" s="16" t="n">
         <v>738</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="D47" s="16" t="n">
         <v>824</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="E47" s="16" t="n">
         <v>764</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="F47" s="16" t="n">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>1868</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B48" s="16" t="n">
         <v>2012</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C48" s="16" t="n">
         <v>1928</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D48" s="16" t="n">
         <v>2207</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="E48" s="16" t="n">
         <v>2195</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>2080</v>
       </c>
     </row>
   </sheetData>
@@ -5339,13 +5526,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -5677,15 +5864,15 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>'balance_raw_33054173'!$F$8</f>
+        <f>'balance_raw_33054173'!$F$11</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>'balance_raw_33054173'!$E$8</f>
+        <f>'balance_raw_33054173'!$E$11</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>'balance_raw_33054173'!$D$8</f>
+        <f>'balance_raw_33054173'!$D$11</f>
         <v/>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -5701,15 +5888,15 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>'balance_raw_33054173'!$F$23</f>
+        <f>'balance_raw_33054173'!$F$26</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>'balance_raw_33054173'!$E$23</f>
+        <f>'balance_raw_33054173'!$E$26</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>'balance_raw_33054173'!$D$23</f>
+        <f>'balance_raw_33054173'!$D$26</f>
         <v/>
       </c>
       <c r="F20" s="25" t="inlineStr">
@@ -5756,15 +5943,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw_33054173'!$F$31</f>
+        <f>'balance_raw_33054173'!$F$34</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw_33054173'!$E$31</f>
+        <f>'balance_raw_33054173'!$E$34</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw_33054173'!$D$31</f>
+        <f>'balance_raw_33054173'!$D$34</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -5780,15 +5967,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_33054173'!$F$45-'balance_raw_33054173'!$F$31</f>
+        <f>'balance_raw_33054173'!$F$48-'balance_raw_33054173'!$F$34</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_33054173'!$E$45-'balance_raw_33054173'!$E$31</f>
+        <f>'balance_raw_33054173'!$E$48-'balance_raw_33054173'!$E$34</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_33054173'!$D$45-'balance_raw_33054173'!$D$31</f>
+        <f>'balance_raw_33054173'!$D$48-'balance_raw_33054173'!$D$34</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -5846,15 +6033,15 @@
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw_33054173'!$F$12</f>
+        <f>'balance_raw_33054173'!$F$15</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw_33054173'!$E$12</f>
+        <f>'balance_raw_33054173'!$E$15</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw_33054173'!$D$12</f>
+        <f>'balance_raw_33054173'!$D$15</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -5870,15 +6057,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw_33054173'!$F$13</f>
+        <f>'balance_raw_33054173'!$F$16</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw_33054173'!$E$13</f>
+        <f>'balance_raw_33054173'!$E$16</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw_33054173'!$D$13</f>
+        <f>'balance_raw_33054173'!$D$16</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -5894,15 +6081,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_33054173'!$F$43</f>
+        <f>'balance_raw_33054173'!$F$46</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_33054173'!$E$43</f>
+        <f>'balance_raw_33054173'!$E$46</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_33054173'!$D$43</f>
+        <f>'balance_raw_33054173'!$D$46</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6059,7 +6246,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6177,7 +6364,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6353,7 +6540,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -6386,15 +6573,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_33054173'!$F$24="","—",IF(ABS(B21-'balance_raw_33054173'!$F$24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_33054173'!$F$24,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_33054173'!$F$27="","—",IF(ABS(B21-'balance_raw_33054173'!$F$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_33054173'!$F$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_33054173'!$E$24="","—",IF(ABS(C21-'balance_raw_33054173'!$E$24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_33054173'!$E$24,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_33054173'!$E$27="","—",IF(ABS(C21-'balance_raw_33054173'!$E$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_33054173'!$E$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_33054173'!$D$24="","—",IF(ABS(D21-'balance_raw_33054173'!$D$24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_33054173'!$D$24,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_33054173'!$D$27="","—",IF(ABS(D21-'balance_raw_33054173'!$D$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_33054173'!$D$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6410,15 +6597,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_33054173'!$F$45="","—",IF(ABS(B25-'balance_raw_33054173'!$F$45)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_33054173'!$F$45,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_33054173'!$F$48="","—",IF(ABS(B25-'balance_raw_33054173'!$F$48)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_33054173'!$F$48,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_33054173'!$E$45="","—",IF(ABS(C25-'balance_raw_33054173'!$E$45)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_33054173'!$E$45,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_33054173'!$E$48="","—",IF(ABS(C25-'balance_raw_33054173'!$E$48)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_33054173'!$E$48,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_33054173'!$D$45="","—",IF(ABS(D25-'balance_raw_33054173'!$D$45)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_33054173'!$D$45,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_33054173'!$D$48="","—",IF(ABS(D25-'balance_raw_33054173'!$D$48)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_33054173'!$D$48,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
